--- a/artfynd/A 25022-2026 artfynd.xlsx
+++ b/artfynd/A 25022-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,69 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>63445726</v>
+        <v>54856026</v>
       </c>
       <c r="B2" t="n">
-        <v>98647</v>
+        <v>43219</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219798</v>
+        <v>201028</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Mindre tåtelsmygare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Thymelicus lineola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Ochsenheimer, 1808)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>600m SSO Svartesjö, Sk</t>
+          <t>Dunge längs Rockarpsvägen, Björkesåkrasjön, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>401404</v>
+        <v>401420</v>
       </c>
       <c r="R2" t="n">
-        <v>6152831</v>
+        <v>6152910</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +761,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2001-07-02</t>
+          <t>2015-08-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2001-07-02</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Epipactis helleborine/2D1a1105/Börringe s:n/GWt/ /Göran Wendt,Växjö</t>
+          <t>2015-08-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,44 +778,25 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>vägren-bokbryn, 4 ex</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>SkFlora    681954</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Kaj Svahn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Göran Wendt</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Skånes Flora (1989-2006)</t>
-        </is>
-      </c>
+          <t>Kaj Svahn</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>66405261</v>
+        <v>63445726</v>
       </c>
       <c r="B3" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -825,26 +822,19 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Dunge längs Rockarpsvägen, Björkesåkrasjön, Sk</t>
+          <t>600m SSO Svartesjö, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>401420.3520107483</v>
+        <v>401404</v>
       </c>
       <c r="R3" t="n">
-        <v>6152910.400268312</v>
+        <v>6152831</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,22 +858,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-06-25</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2001-07-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-06-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2001-07-02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine/2D1a1105/Börringe s:n/GWt/ /Göran Wendt,Växjö</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,18 +880,136 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>vägren-bokbryn, 4 ex</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>SkFlora    681954</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Göran Wendt</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Skånes Flora (1989-2006)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>66405261</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Dunge längs Rockarpsvägen, Björkesåkrasjön, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>401420</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6152910</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Svedala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Börringe</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2017-06-25</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2017-06-25</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Kaj Svahn</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Kaj Svahn</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25022-2026 artfynd.xlsx
+++ b/artfynd/A 25022-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -790,6 +795,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54856026</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,6 +916,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63445726</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1010,8 +1025,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66405261</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>